--- a/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_6_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_6_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.24318</v>
+        <v>0.246284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.530435</v>
+        <v>0.537915</v>
       </c>
       <c r="H2" t="n">
-        <v>0.478431</v>
+        <v>0.296732</v>
       </c>
       <c r="I2" t="n">
-        <v>0.503093</v>
+        <v>0.382477</v>
       </c>
       <c r="J2" t="n">
-        <v>0.258025</v>
+        <v>0.255969</v>
       </c>
       <c r="K2" t="n">
-        <v>0.459184</v>
+        <v>0.452174</v>
       </c>
       <c r="L2" t="n">
-        <v>0.456853</v>
+        <v>0.263959</v>
       </c>
       <c r="M2" t="n">
-        <v>0.458015</v>
+        <v>0.333333</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_12.txt</t>
+          <t>_2_3_3_1_1790730949_15.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
       </c>
       <c r="AA2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.242337</v>
+        <v>0.242331</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.532836</v>
+        <v>0.53621</v>
       </c>
       <c r="H3" t="n">
-        <v>0.466667</v>
+        <v>0.454902</v>
       </c>
       <c r="I3" t="n">
-        <v>0.497561</v>
+        <v>0.492221</v>
       </c>
       <c r="J3" t="n">
-        <v>0.256965</v>
+        <v>0.258064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.47027</v>
+        <v>0.470588</v>
       </c>
       <c r="L3" t="n">
-        <v>0.441624</v>
+        <v>0.446701</v>
       </c>
       <c r="M3" t="n">
-        <v>0.455497</v>
+        <v>0.458333</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_6.txt</t>
+          <t>_2_6_1_1790730902_0.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.246704</v>
+        <v>0.24318</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.496454</v>
+        <v>0.530435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.183007</v>
+        <v>0.478431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.267431</v>
+        <v>0.503093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.252079</v>
+        <v>0.258025</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4</v>
+        <v>0.459184</v>
       </c>
       <c r="L4" t="n">
-        <v>0.152284</v>
+        <v>0.456853</v>
       </c>
       <c r="M4" t="n">
-        <v>0.220588</v>
+        <v>0.458015</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_7.txt</t>
+          <t>_2_6_1_1790730902_12.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>6</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.242506</v>
+        <v>0.244348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5460120000000001</v>
+        <v>0.556237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.465359</v>
+        <v>0.355556</v>
       </c>
       <c r="I5" t="n">
-        <v>0.50247</v>
+        <v>0.433812</v>
       </c>
       <c r="J5" t="n">
-        <v>0.257081</v>
+        <v>0.256012</v>
       </c>
       <c r="K5" t="n">
-        <v>0.472826</v>
+        <v>0.503817</v>
       </c>
       <c r="L5" t="n">
-        <v>0.441624</v>
+        <v>0.335025</v>
       </c>
       <c r="M5" t="n">
-        <v>0.456693</v>
+        <v>0.402439</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_3.txt</t>
+          <t>_2_3_3_1_1790730949_3.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>6</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,7 +985,7 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.248052</v>
+        <v>0.24445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571072</v>
+        <v>0.54703</v>
       </c>
       <c r="H6" t="n">
-        <v>0.299346</v>
+        <v>0.288889</v>
       </c>
       <c r="I6" t="n">
-        <v>0.392796</v>
+        <v>0.378101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25278</v>
+        <v>0.254552</v>
       </c>
       <c r="K6" t="n">
-        <v>0.476636</v>
+        <v>0.457944</v>
       </c>
       <c r="L6" t="n">
-        <v>0.258883</v>
+        <v>0.248731</v>
       </c>
       <c r="M6" t="n">
-        <v>0.335526</v>
+        <v>0.322368</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_19.txt</t>
+          <t>_2_3_3_1_1790730949_9.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1086,7 +1086,7 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.242329</v>
+        <v>0.242305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.537202</v>
+        <v>0.540936</v>
       </c>
       <c r="H7" t="n">
-        <v>0.471895</v>
+        <v>0.48366</v>
       </c>
       <c r="I7" t="n">
-        <v>0.502436</v>
+        <v>0.510697</v>
       </c>
       <c r="J7" t="n">
-        <v>0.256872</v>
+        <v>0.256905</v>
       </c>
       <c r="K7" t="n">
-        <v>0.465969</v>
+        <v>0.466667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.451777</v>
+        <v>0.461929</v>
       </c>
       <c r="M7" t="n">
-        <v>0.458763</v>
+        <v>0.464286</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_7.txt</t>
+          <t>_2_6_1_1790730902_10.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.242328</v>
+        <v>0.246724</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5411589999999999</v>
+        <v>0.488136</v>
       </c>
       <c r="H8" t="n">
-        <v>0.464052</v>
+        <v>0.188235</v>
       </c>
       <c r="I8" t="n">
-        <v>0.499648</v>
+        <v>0.271698</v>
       </c>
       <c r="J8" t="n">
-        <v>0.25846</v>
+        <v>0.25249</v>
       </c>
       <c r="K8" t="n">
-        <v>0.465517</v>
+        <v>0.410256</v>
       </c>
       <c r="L8" t="n">
-        <v>0.411168</v>
+        <v>0.162437</v>
       </c>
       <c r="M8" t="n">
-        <v>0.436658</v>
+        <v>0.232727</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_13.txt</t>
+          <t>_2_3_3_1_1790730949_6.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>6</v>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.246737</v>
+        <v>0.246783</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.502976</v>
+        <v>0.520325</v>
       </c>
       <c r="H9" t="n">
-        <v>0.220915</v>
+        <v>0.25098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.306994</v>
+        <v>0.338624</v>
       </c>
       <c r="J9" t="n">
-        <v>0.252524</v>
+        <v>0.252439</v>
       </c>
       <c r="K9" t="n">
-        <v>0.41573</v>
+        <v>0.425743</v>
       </c>
       <c r="L9" t="n">
-        <v>0.187817</v>
+        <v>0.218274</v>
       </c>
       <c r="M9" t="n">
-        <v>0.258741</v>
+        <v>0.288591</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_14.txt</t>
+          <t>_2_3_3_1_1790730949_17.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,42 +1389,42 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.246864</v>
+        <v>0.242388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.508532</v>
+        <v>0.540335</v>
       </c>
       <c r="H10" t="n">
-        <v>0.194771</v>
+        <v>0.464052</v>
       </c>
       <c r="I10" t="n">
-        <v>0.281664</v>
+        <v>0.499297</v>
       </c>
       <c r="J10" t="n">
-        <v>0.251246</v>
+        <v>0.257377</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444444</v>
+        <v>0.478261</v>
       </c>
       <c r="L10" t="n">
-        <v>0.182741</v>
+        <v>0.446701</v>
       </c>
       <c r="M10" t="n">
-        <v>0.258993</v>
+        <v>0.461942</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,23 +1460,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_10.txt</t>
+          <t>_2_6_1_1790730902_16.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>6</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.246819</v>
+        <v>0.242489</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.501706</v>
+        <v>0.541411</v>
       </c>
       <c r="H11" t="n">
-        <v>0.192157</v>
+        <v>0.461438</v>
       </c>
       <c r="I11" t="n">
-        <v>0.277883</v>
+        <v>0.498236</v>
       </c>
       <c r="J11" t="n">
-        <v>0.252696</v>
+        <v>0.258811</v>
       </c>
       <c r="K11" t="n">
-        <v>0.409639</v>
+        <v>0.46114</v>
       </c>
       <c r="L11" t="n">
-        <v>0.172589</v>
+        <v>0.451777</v>
       </c>
       <c r="M11" t="n">
-        <v>0.242857</v>
+        <v>0.45641</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,23 +1561,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_0.txt</t>
+          <t>_2_6_1_1790730902_2.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>6</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1591,7 +1591,7 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.244285</v>
+        <v>0.246751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.548736</v>
+        <v>0.49375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.397386</v>
+        <v>0.206536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.460955</v>
+        <v>0.291244</v>
       </c>
       <c r="J12" t="n">
-        <v>0.255867</v>
+        <v>0.252549</v>
       </c>
       <c r="K12" t="n">
-        <v>0.458333</v>
+        <v>0.421687</v>
       </c>
       <c r="L12" t="n">
-        <v>0.335025</v>
+        <v>0.177665</v>
       </c>
       <c r="M12" t="n">
-        <v>0.387097</v>
+        <v>0.25</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_18.txt</t>
+          <t>_2_3_3_1_1790730949_4.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.24445</v>
+        <v>0.244285</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.54703</v>
+        <v>0.548736</v>
       </c>
       <c r="H13" t="n">
-        <v>0.288889</v>
+        <v>0.397386</v>
       </c>
       <c r="I13" t="n">
-        <v>0.378101</v>
+        <v>0.460955</v>
       </c>
       <c r="J13" t="n">
-        <v>0.254552</v>
+        <v>0.255867</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457944</v>
+        <v>0.458333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.248731</v>
+        <v>0.335025</v>
       </c>
       <c r="M13" t="n">
-        <v>0.322368</v>
+        <v>0.387097</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_9.txt</t>
+          <t>_2_3_3_1_1790730949_18.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1793,42 +1793,42 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.242354</v>
+        <v>0.246737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.540984</v>
+        <v>0.502976</v>
       </c>
       <c r="H14" t="n">
-        <v>0.47451</v>
+        <v>0.220915</v>
       </c>
       <c r="I14" t="n">
-        <v>0.505571</v>
+        <v>0.306994</v>
       </c>
       <c r="J14" t="n">
-        <v>0.258406</v>
+        <v>0.252524</v>
       </c>
       <c r="K14" t="n">
-        <v>0.467742</v>
+        <v>0.41573</v>
       </c>
       <c r="L14" t="n">
-        <v>0.441624</v>
+        <v>0.187817</v>
       </c>
       <c r="M14" t="n">
-        <v>0.454308</v>
+        <v>0.258741</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_8.txt</t>
+          <t>_2_3_3_1_1790730949_14.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>6</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.245469</v>
+        <v>0.246871</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.52</v>
+        <v>0.504983</v>
       </c>
       <c r="H15" t="n">
-        <v>0.356863</v>
+        <v>0.198693</v>
       </c>
       <c r="I15" t="n">
-        <v>0.423256</v>
+        <v>0.285178</v>
       </c>
       <c r="J15" t="n">
-        <v>0.254512</v>
+        <v>0.252431</v>
       </c>
       <c r="K15" t="n">
-        <v>0.470588</v>
+        <v>0.416667</v>
       </c>
       <c r="L15" t="n">
-        <v>0.365482</v>
+        <v>0.177665</v>
       </c>
       <c r="M15" t="n">
-        <v>0.411429</v>
+        <v>0.24911</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_13.txt</t>
+          <t>_2_3_3_1_1790730949_8.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1995,42 +1995,42 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.247097</v>
+        <v>0.242328</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F16" t="n">
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.536111</v>
+        <v>0.5411589999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.252288</v>
+        <v>0.464052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.343111</v>
+        <v>0.499648</v>
       </c>
       <c r="J16" t="n">
-        <v>0.251722</v>
+        <v>0.25846</v>
       </c>
       <c r="K16" t="n">
-        <v>0.465347</v>
+        <v>0.465517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.238579</v>
+        <v>0.411168</v>
       </c>
       <c r="M16" t="n">
-        <v>0.315436</v>
+        <v>0.436658</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,23 +2066,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_11.txt</t>
+          <t>_2_6_1_1790730902_13.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z16" t="n">
         <v>6</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.245488</v>
+        <v>0.24636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.542411</v>
+        <v>0.52443</v>
       </c>
       <c r="H17" t="n">
-        <v>0.317647</v>
+        <v>0.210458</v>
       </c>
       <c r="I17" t="n">
-        <v>0.40066</v>
+        <v>0.300373</v>
       </c>
       <c r="J17" t="n">
-        <v>0.251929</v>
+        <v>0.252396</v>
       </c>
       <c r="K17" t="n">
-        <v>0.472441</v>
+        <v>0.436782</v>
       </c>
       <c r="L17" t="n">
-        <v>0.304569</v>
+        <v>0.192893</v>
       </c>
       <c r="M17" t="n">
-        <v>0.37037</v>
+        <v>0.267606</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_12.txt</t>
+          <t>_2_3_3_1_1790730949_16.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.244348</v>
+        <v>0.245469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556237</v>
+        <v>0.52</v>
       </c>
       <c r="H18" t="n">
-        <v>0.355556</v>
+        <v>0.356863</v>
       </c>
       <c r="I18" t="n">
-        <v>0.433812</v>
+        <v>0.423256</v>
       </c>
       <c r="J18" t="n">
-        <v>0.256012</v>
+        <v>0.254512</v>
       </c>
       <c r="K18" t="n">
-        <v>0.503817</v>
+        <v>0.470588</v>
       </c>
       <c r="L18" t="n">
-        <v>0.335025</v>
+        <v>0.365482</v>
       </c>
       <c r="M18" t="n">
-        <v>0.402439</v>
+        <v>0.411429</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_3.txt</t>
+          <t>_2_3_3_1_1790730949_13.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2298,42 +2298,42 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.242489</v>
+        <v>0.248052</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.541411</v>
+        <v>0.571072</v>
       </c>
       <c r="H19" t="n">
-        <v>0.461438</v>
+        <v>0.299346</v>
       </c>
       <c r="I19" t="n">
-        <v>0.498236</v>
+        <v>0.392796</v>
       </c>
       <c r="J19" t="n">
-        <v>0.258811</v>
+        <v>0.25278</v>
       </c>
       <c r="K19" t="n">
-        <v>0.46114</v>
+        <v>0.476636</v>
       </c>
       <c r="L19" t="n">
-        <v>0.451777</v>
+        <v>0.258883</v>
       </c>
       <c r="M19" t="n">
-        <v>0.45641</v>
+        <v>0.335526</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,23 +2369,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_2.txt</t>
+          <t>_2_3_3_1_1790730949_19.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>6</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2399,42 +2399,42 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.244245</v>
+        <v>0.242203</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5577260000000001</v>
+        <v>0.53429</v>
       </c>
       <c r="H20" t="n">
-        <v>0.410458</v>
+        <v>0.437909</v>
       </c>
       <c r="I20" t="n">
-        <v>0.472892</v>
+        <v>0.481322</v>
       </c>
       <c r="J20" t="n">
-        <v>0.254795</v>
+        <v>0.257671</v>
       </c>
       <c r="K20" t="n">
-        <v>0.519481</v>
+        <v>0.478723</v>
       </c>
       <c r="L20" t="n">
-        <v>0.406091</v>
+        <v>0.456853</v>
       </c>
       <c r="M20" t="n">
-        <v>0.45584</v>
+        <v>0.467532</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,23 +2470,23 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_1.txt</t>
+          <t>_2_6_1_1790730902_18.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z20" t="n">
         <v>6</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2500,7 +2500,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.242343</v>
+        <v>0.242545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.538346</v>
+        <v>0.533937</v>
       </c>
       <c r="H21" t="n">
-        <v>0.467974</v>
+        <v>0.462745</v>
       </c>
       <c r="I21" t="n">
-        <v>0.500699</v>
+        <v>0.495798</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25845</v>
+        <v>0.257157</v>
       </c>
       <c r="K21" t="n">
-        <v>0.458564</v>
+        <v>0.469613</v>
       </c>
       <c r="L21" t="n">
-        <v>0.42132</v>
+        <v>0.431472</v>
       </c>
       <c r="M21" t="n">
-        <v>0.439153</v>
+        <v>0.449735</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_15.txt</t>
+          <t>_2_6_1_1790730902_14.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.242789</v>
+        <v>0.242423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2618,25 +2618,25 @@
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.555725</v>
+        <v>0.542683</v>
       </c>
       <c r="H22" t="n">
-        <v>0.475817</v>
+        <v>0.465359</v>
       </c>
       <c r="I22" t="n">
-        <v>0.512676</v>
+        <v>0.5010559999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.258842</v>
+        <v>0.257328</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475936</v>
+        <v>0.472826</v>
       </c>
       <c r="L22" t="n">
-        <v>0.451777</v>
+        <v>0.441624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.463542</v>
+        <v>0.456693</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_19.txt</t>
+          <t>_2_6_1_1790730902_4.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.242426</v>
+        <v>0.246864</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.537954</v>
+        <v>0.508532</v>
       </c>
       <c r="H23" t="n">
-        <v>0.426144</v>
+        <v>0.194771</v>
       </c>
       <c r="I23" t="n">
-        <v>0.475565</v>
+        <v>0.281664</v>
       </c>
       <c r="J23" t="n">
-        <v>0.25835</v>
+        <v>0.251246</v>
       </c>
       <c r="K23" t="n">
-        <v>0.469512</v>
+        <v>0.444444</v>
       </c>
       <c r="L23" t="n">
-        <v>0.390863</v>
+        <v>0.182741</v>
       </c>
       <c r="M23" t="n">
-        <v>0.426593</v>
+        <v>0.258993</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_9.txt</t>
+          <t>_2_3_3_1_1790730949_10.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>6</v>
       </c>
       <c r="AA23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.242342</v>
+        <v>0.242354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.540785</v>
+        <v>0.540984</v>
       </c>
       <c r="H24" t="n">
-        <v>0.467974</v>
+        <v>0.47451</v>
       </c>
       <c r="I24" t="n">
-        <v>0.501752</v>
+        <v>0.505571</v>
       </c>
       <c r="J24" t="n">
-        <v>0.258416</v>
+        <v>0.258406</v>
       </c>
       <c r="K24" t="n">
-        <v>0.457627</v>
+        <v>0.467742</v>
       </c>
       <c r="L24" t="n">
-        <v>0.411168</v>
+        <v>0.441624</v>
       </c>
       <c r="M24" t="n">
-        <v>0.433155</v>
+        <v>0.454308</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_1.txt</t>
+          <t>_2_6_1_1790730902_8.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2904,7 +2904,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.242331</v>
+        <v>0.242789</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.53621</v>
+        <v>0.555725</v>
       </c>
       <c r="H25" t="n">
-        <v>0.454902</v>
+        <v>0.475817</v>
       </c>
       <c r="I25" t="n">
-        <v>0.492221</v>
+        <v>0.512676</v>
       </c>
       <c r="J25" t="n">
-        <v>0.258064</v>
+        <v>0.258842</v>
       </c>
       <c r="K25" t="n">
-        <v>0.470588</v>
+        <v>0.475936</v>
       </c>
       <c r="L25" t="n">
-        <v>0.446701</v>
+        <v>0.451777</v>
       </c>
       <c r="M25" t="n">
-        <v>0.458333</v>
+        <v>0.463542</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_0.txt</t>
+          <t>_2_6_1_1790730902_19.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3005,7 +3005,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.24636</v>
+        <v>0.244676</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3022,25 +3022,25 @@
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.52443</v>
+        <v>0.5386</v>
       </c>
       <c r="H26" t="n">
-        <v>0.210458</v>
+        <v>0.392157</v>
       </c>
       <c r="I26" t="n">
-        <v>0.300373</v>
+        <v>0.453858</v>
       </c>
       <c r="J26" t="n">
-        <v>0.252396</v>
+        <v>0.255661</v>
       </c>
       <c r="K26" t="n">
-        <v>0.436782</v>
+        <v>0.450331</v>
       </c>
       <c r="L26" t="n">
-        <v>0.192893</v>
+        <v>0.345178</v>
       </c>
       <c r="M26" t="n">
-        <v>0.267606</v>
+        <v>0.390805</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_16.txt</t>
+          <t>_2_3_3_1_1790730949_2.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.242203</v>
+        <v>0.242506</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.53429</v>
+        <v>0.5460120000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.437909</v>
+        <v>0.465359</v>
       </c>
       <c r="I27" t="n">
-        <v>0.481322</v>
+        <v>0.50247</v>
       </c>
       <c r="J27" t="n">
-        <v>0.257671</v>
+        <v>0.257081</v>
       </c>
       <c r="K27" t="n">
-        <v>0.478723</v>
+        <v>0.472826</v>
       </c>
       <c r="L27" t="n">
-        <v>0.456853</v>
+        <v>0.441624</v>
       </c>
       <c r="M27" t="n">
-        <v>0.467532</v>
+        <v>0.456693</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_18.txt</t>
+          <t>_2_6_1_1790730902_3.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.246724</v>
+        <v>0.244245</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.488136</v>
+        <v>0.5577260000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.188235</v>
+        <v>0.410458</v>
       </c>
       <c r="I28" t="n">
-        <v>0.271698</v>
+        <v>0.472892</v>
       </c>
       <c r="J28" t="n">
-        <v>0.25249</v>
+        <v>0.254795</v>
       </c>
       <c r="K28" t="n">
-        <v>0.410256</v>
+        <v>0.519481</v>
       </c>
       <c r="L28" t="n">
-        <v>0.162437</v>
+        <v>0.406091</v>
       </c>
       <c r="M28" t="n">
-        <v>0.232727</v>
+        <v>0.45584</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_6.txt</t>
+          <t>_2_3_3_1_1790730949_1.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.242423</v>
+        <v>0.242342</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.542683</v>
+        <v>0.540785</v>
       </c>
       <c r="H29" t="n">
-        <v>0.465359</v>
+        <v>0.467974</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5010559999999999</v>
+        <v>0.501752</v>
       </c>
       <c r="J29" t="n">
-        <v>0.257328</v>
+        <v>0.258416</v>
       </c>
       <c r="K29" t="n">
-        <v>0.472826</v>
+        <v>0.457627</v>
       </c>
       <c r="L29" t="n">
-        <v>0.441624</v>
+        <v>0.411168</v>
       </c>
       <c r="M29" t="n">
-        <v>0.456693</v>
+        <v>0.433155</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_4.txt</t>
+          <t>_2_6_1_1790730902_1.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,7 +3409,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.242545</v>
+        <v>0.242329</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3426,25 +3426,25 @@
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.533937</v>
+        <v>0.537202</v>
       </c>
       <c r="H30" t="n">
-        <v>0.462745</v>
+        <v>0.471895</v>
       </c>
       <c r="I30" t="n">
-        <v>0.495798</v>
+        <v>0.502436</v>
       </c>
       <c r="J30" t="n">
-        <v>0.257157</v>
+        <v>0.256872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.469613</v>
+        <v>0.465969</v>
       </c>
       <c r="L30" t="n">
-        <v>0.431472</v>
+        <v>0.451777</v>
       </c>
       <c r="M30" t="n">
-        <v>0.449735</v>
+        <v>0.458763</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_14.txt</t>
+          <t>_2_6_1_1790730902_7.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3510,7 +3510,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.242388</v>
+        <v>0.242343</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3527,25 +3527,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.540335</v>
+        <v>0.538346</v>
       </c>
       <c r="H31" t="n">
-        <v>0.464052</v>
+        <v>0.467974</v>
       </c>
       <c r="I31" t="n">
-        <v>0.499297</v>
+        <v>0.500699</v>
       </c>
       <c r="J31" t="n">
-        <v>0.257377</v>
+        <v>0.25845</v>
       </c>
       <c r="K31" t="n">
-        <v>0.478261</v>
+        <v>0.458564</v>
       </c>
       <c r="L31" t="n">
-        <v>0.446701</v>
+        <v>0.42132</v>
       </c>
       <c r="M31" t="n">
-        <v>0.461942</v>
+        <v>0.439153</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_16.txt</t>
+          <t>_2_6_1_1790730902_15.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.246751</v>
+        <v>0.242426</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E32" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.49375</v>
+        <v>0.537954</v>
       </c>
       <c r="H32" t="n">
-        <v>0.206536</v>
+        <v>0.426144</v>
       </c>
       <c r="I32" t="n">
-        <v>0.291244</v>
+        <v>0.475565</v>
       </c>
       <c r="J32" t="n">
-        <v>0.252549</v>
+        <v>0.25835</v>
       </c>
       <c r="K32" t="n">
-        <v>0.421687</v>
+        <v>0.469512</v>
       </c>
       <c r="L32" t="n">
-        <v>0.177665</v>
+        <v>0.390863</v>
       </c>
       <c r="M32" t="n">
-        <v>0.25</v>
+        <v>0.426593</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_4.txt</t>
+          <t>_2_6_1_1790730902_9.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>6</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.244505</v>
+        <v>0.246819</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3729,25 +3729,25 @@
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.539499</v>
+        <v>0.501706</v>
       </c>
       <c r="H33" t="n">
-        <v>0.366013</v>
+        <v>0.192157</v>
       </c>
       <c r="I33" t="n">
-        <v>0.436137</v>
+        <v>0.277883</v>
       </c>
       <c r="J33" t="n">
-        <v>0.25599</v>
+        <v>0.252696</v>
       </c>
       <c r="K33" t="n">
-        <v>0.467626</v>
+        <v>0.409639</v>
       </c>
       <c r="L33" t="n">
-        <v>0.329949</v>
+        <v>0.172589</v>
       </c>
       <c r="M33" t="n">
-        <v>0.386905</v>
+        <v>0.242857</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_5.txt</t>
+          <t>_2_3_3_1_1790730949_0.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.242305</v>
+        <v>0.242404</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.540936</v>
+        <v>0.548435</v>
       </c>
       <c r="H34" t="n">
-        <v>0.48366</v>
+        <v>0.481046</v>
       </c>
       <c r="I34" t="n">
-        <v>0.510697</v>
+        <v>0.512535</v>
       </c>
       <c r="J34" t="n">
-        <v>0.256905</v>
+        <v>0.25698</v>
       </c>
       <c r="K34" t="n">
-        <v>0.466667</v>
+        <v>0.47644</v>
       </c>
       <c r="L34" t="n">
         <v>0.461929</v>
       </c>
       <c r="M34" t="n">
-        <v>0.464286</v>
+        <v>0.469072</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_10.txt</t>
+          <t>_2_6_1_1790730902_17.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3914,42 +3914,42 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.243902</v>
+        <v>0.246704</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E35" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.550725</v>
+        <v>0.496454</v>
       </c>
       <c r="H35" t="n">
-        <v>0.397386</v>
+        <v>0.183007</v>
       </c>
       <c r="I35" t="n">
-        <v>0.461655</v>
+        <v>0.267431</v>
       </c>
       <c r="J35" t="n">
-        <v>0.255977</v>
+        <v>0.252079</v>
       </c>
       <c r="K35" t="n">
-        <v>0.453333</v>
+        <v>0.4</v>
       </c>
       <c r="L35" t="n">
-        <v>0.345178</v>
+        <v>0.152284</v>
       </c>
       <c r="M35" t="n">
-        <v>0.391931</v>
+        <v>0.220588</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,23 +3985,23 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_5.txt</t>
+          <t>_2_3_3_1_1790730949_7.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>6</v>
       </c>
       <c r="AA35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.244676</v>
+        <v>0.247097</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5386</v>
+        <v>0.536111</v>
       </c>
       <c r="H36" t="n">
-        <v>0.392157</v>
+        <v>0.252288</v>
       </c>
       <c r="I36" t="n">
-        <v>0.453858</v>
+        <v>0.343111</v>
       </c>
       <c r="J36" t="n">
-        <v>0.255661</v>
+        <v>0.251722</v>
       </c>
       <c r="K36" t="n">
-        <v>0.450331</v>
+        <v>0.465347</v>
       </c>
       <c r="L36" t="n">
-        <v>0.345178</v>
+        <v>0.238579</v>
       </c>
       <c r="M36" t="n">
-        <v>0.390805</v>
+        <v>0.315436</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_2.txt</t>
+          <t>_2_3_3_1_1790730949_11.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4116,42 +4116,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.246783</v>
+        <v>0.242337</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E37" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.520325</v>
+        <v>0.532836</v>
       </c>
       <c r="H37" t="n">
-        <v>0.25098</v>
+        <v>0.466667</v>
       </c>
       <c r="I37" t="n">
-        <v>0.338624</v>
+        <v>0.497561</v>
       </c>
       <c r="J37" t="n">
-        <v>0.252439</v>
+        <v>0.256965</v>
       </c>
       <c r="K37" t="n">
-        <v>0.425743</v>
+        <v>0.47027</v>
       </c>
       <c r="L37" t="n">
-        <v>0.218274</v>
+        <v>0.441624</v>
       </c>
       <c r="M37" t="n">
-        <v>0.288591</v>
+        <v>0.455497</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,23 +4187,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_17.txt</t>
+          <t>_2_6_1_1790730902_6.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>6</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4217,42 +4217,42 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.246284</v>
+        <v>0.242321</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1790730949</v>
+        <v>1790730902</v>
       </c>
       <c r="E38" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F38" t="n">
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537915</v>
+        <v>0.544361</v>
       </c>
       <c r="H38" t="n">
-        <v>0.296732</v>
+        <v>0.473203</v>
       </c>
       <c r="I38" t="n">
-        <v>0.382477</v>
+        <v>0.506294</v>
       </c>
       <c r="J38" t="n">
-        <v>0.255969</v>
+        <v>0.258356</v>
       </c>
       <c r="K38" t="n">
-        <v>0.452174</v>
+        <v>0.475936</v>
       </c>
       <c r="L38" t="n">
-        <v>0.263959</v>
+        <v>0.451777</v>
       </c>
       <c r="M38" t="n">
-        <v>0.333333</v>
+        <v>0.463542</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,23 +4288,23 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_15.txt</t>
+          <t>_2_6_1_1790730902_11.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z38" t="n">
         <v>6</v>
       </c>
       <c r="AA38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4318,7 +4318,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.242404</v>
+        <v>0.243902</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4335,25 +4335,25 @@
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.548435</v>
+        <v>0.550725</v>
       </c>
       <c r="H39" t="n">
-        <v>0.481046</v>
+        <v>0.397386</v>
       </c>
       <c r="I39" t="n">
-        <v>0.512535</v>
+        <v>0.461655</v>
       </c>
       <c r="J39" t="n">
-        <v>0.25698</v>
+        <v>0.255977</v>
       </c>
       <c r="K39" t="n">
-        <v>0.47644</v>
+        <v>0.453333</v>
       </c>
       <c r="L39" t="n">
-        <v>0.461929</v>
+        <v>0.345178</v>
       </c>
       <c r="M39" t="n">
-        <v>0.469072</v>
+        <v>0.391931</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_17.txt</t>
+          <t>_2_6_1_1790730902_5.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.246871</v>
+        <v>0.245488</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.504983</v>
+        <v>0.542411</v>
       </c>
       <c r="H40" t="n">
-        <v>0.198693</v>
+        <v>0.317647</v>
       </c>
       <c r="I40" t="n">
-        <v>0.285178</v>
+        <v>0.40066</v>
       </c>
       <c r="J40" t="n">
-        <v>0.252431</v>
+        <v>0.251929</v>
       </c>
       <c r="K40" t="n">
-        <v>0.416667</v>
+        <v>0.472441</v>
       </c>
       <c r="L40" t="n">
-        <v>0.177665</v>
+        <v>0.304569</v>
       </c>
       <c r="M40" t="n">
-        <v>0.24911</v>
+        <v>0.37037</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790730949_8.txt</t>
+          <t>_2_3_3_1_1790730949_12.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.242321</v>
+        <v>0.244505</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790730902</v>
+        <v>1790730949</v>
       </c>
       <c r="E41" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.544361</v>
+        <v>0.539499</v>
       </c>
       <c r="H41" t="n">
-        <v>0.473203</v>
+        <v>0.366013</v>
       </c>
       <c r="I41" t="n">
-        <v>0.506294</v>
+        <v>0.436137</v>
       </c>
       <c r="J41" t="n">
-        <v>0.258356</v>
+        <v>0.25599</v>
       </c>
       <c r="K41" t="n">
-        <v>0.475936</v>
+        <v>0.467626</v>
       </c>
       <c r="L41" t="n">
-        <v>0.451777</v>
+        <v>0.329949</v>
       </c>
       <c r="M41" t="n">
-        <v>0.463542</v>
+        <v>0.386905</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_6_1_1790730902_11.txt</t>
+          <t>_2_3_3_1_1790730949_5.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.31903805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07076477577489422</v>
+        <v>0.07076477577489419</v>
       </c>
       <c r="D2" t="n">
         <v>0.45584</v>
